--- a/CB_HSI_MAPPING/testing_final/Input/cubiX-SGMW - System Requirements.xlsx
+++ b/CB_HSI_MAPPING/testing_final/Input/cubiX-SGMW - System Requirements.xlsx
@@ -2368,6 +2368,12 @@
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="455088e1-af34-4927-a3f0-bdce59540293">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <PrimeCorrectedByUser xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
+    <testStatus xmlns="455088e1-af34-4927-a3f0-bdce59540293" xsi:nil="true"/>
+    <PrimeClassificationStatusDetails xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
+    <PrimeClassificationStatus xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
+    <PrimeLastClassified xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
+    <PrimeAutofillMeta xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
@@ -2382,8 +2388,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F4ECDE3992A08C4AB27EAAF617A05967" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6030d3fe49356aaef09cec4ad8e6441b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="455088e1-af34-4927-a3f0-bdce59540293" xmlns:ns3="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39cc5a898485895145ac9f4685282a2b" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F4ECDE3992A08C4AB27EAAF617A05967" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9683c085a59988fd2dc84fe522921e1c">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="455088e1-af34-4927-a3f0-bdce59540293" xmlns:ns3="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7184c417cebe2c46bf9076e6fd8b1060" ns2:_="" ns3:_="">
     <xsd:import namespace="455088e1-af34-4927-a3f0-bdce59540293"/>
     <xsd:import namespace="f4ecdb93-bc7f-4438-8c77-236ab96c18a9"/>
     <xsd:element name="properties">
@@ -2403,6 +2409,12 @@
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:testStatus" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeClassificationStatus" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeClassificationStatusDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeLastClassified" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeCorrectedByUser" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeAutofillMeta" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2467,6 +2479,18 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="testStatus" ma:index="20" nillable="true" ma:displayName="Test status" ma:description="Summarizes overall test outcome so failed or mixed-result files can be found quickly." ma:internalName="testStatus">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="Pass"/>
+          <xsd:enumeration value="Fail"/>
+          <xsd:enumeration value="Error"/>
+          <xsd:enumeration value="Skipped"/>
+          <xsd:enumeration value="Mixed"/>
+          <xsd:enumeration value="Not found"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -2481,6 +2505,33 @@
           </xsd:extension>
         </xsd:complexContent>
       </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="PrimeClassificationStatus" ma:index="21" nillable="true" ma:displayName="Processing status" ma:internalName="PrimeClassificationStatus">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PrimeClassificationStatusDetails" ma:index="22" nillable="true" ma:displayName="Processing details" ma:internalName="PrimeClassificationStatusDetails">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PrimeLastClassified" ma:index="23" nillable="true" ma:displayName="Processed" ma:internalName="PrimeLastClassified">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PrimeCorrectedByUser" ma:index="24" nillable="true" ma:displayName="Corrected" ma:internalName="PrimeCorrectedByUser">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PrimeAutofillMeta" ma:index="25" nillable="true" ma:displayName="Autofill Meta" ma:hidden="true" ma:internalName="PrimeAutofillMeta">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -2602,5 +2653,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C401FAA9-0C67-484D-A99E-2D8EF2E01902}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0764FA3-7241-4B34-8FAA-31977B143D0F}"/>
 </file>